--- a/文档/项目组考勤与开发日志.xlsx
+++ b/文档/项目组考勤与开发日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="87">
   <si>
     <t>智慧烟感项目 · 考勤与开发日志表 使用说明</t>
   </si>
@@ -147,6 +147,9 @@
     <t>组长</t>
   </si>
   <si>
+    <t>PM</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -156,12 +159,21 @@
     <t>组员</t>
   </si>
   <si>
+    <t>硬件测试</t>
+  </si>
+  <si>
     <t>郑良锋</t>
   </si>
   <si>
+    <t>后端开发</t>
+  </si>
+  <si>
     <t>陈心澄</t>
   </si>
   <si>
+    <t>前端开发</t>
+  </si>
+  <si>
     <t>王田煜</t>
   </si>
   <si>
@@ -277,6 +289,27 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>设计原型</t>
+  </si>
+  <si>
+    <t>明确各个模块的细节，交互逻辑和API接口</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>进行中</t>
+  </si>
+  <si>
+    <t>下载硬件环境，跑通硬件</t>
+  </si>
+  <si>
+    <t>后端配置环境</t>
+  </si>
+  <si>
+    <t>郑良锋、王田煜</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1549,7 @@
         <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="1:6">
@@ -1524,19 +1557,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7">
         <v>20240640</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="1:6">
@@ -1544,19 +1577,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4">
         <v>20243667</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="1:6">
@@ -1564,19 +1597,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C8" s="7">
         <v>20241428</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="1:6">
@@ -1584,19 +1617,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4">
         <v>20243777</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1625,12 +1658,12 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:10">
@@ -1638,31 +1671,31 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="14.5" spans="1:10">
@@ -1673,28 +1706,28 @@
         <v>46202</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I5" s="4">
         <v>4</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="1:10">
@@ -1705,28 +1738,28 @@
         <v>46202</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I6" s="7">
         <v>4</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="1:10">
@@ -1737,28 +1770,28 @@
         <v>46202</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I7" s="4">
         <v>4</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="1:10">
@@ -1769,28 +1802,28 @@
         <v>46202</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I8" s="7">
         <v>4</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="1:10">
@@ -1801,28 +1834,28 @@
         <v>46202</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I9" s="4">
         <v>4</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="8" customHeight="1" spans="1:10">
@@ -1845,29 +1878,29 @@
         <v>46203</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E11="",0,TIMEVALUE(F11)-TIMEVALUE(E11)))+(IF(G11="",0,TIMEVALUE(H11)-TIMEVALUE(G11))))*24,2),"")</f>
         <v/>
       </c>
       <c r="J11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="1:10">
@@ -1878,29 +1911,29 @@
         <v>46203</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="7" t="str">
         <f>IFERROR(ROUND(((IF(E12="",0,TIMEVALUE(F12)-TIMEVALUE(E12)))+(IF(G12="",0,TIMEVALUE(H12)-TIMEVALUE(G12))))*24,2),"")</f>
         <v/>
       </c>
       <c r="J12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:10">
@@ -1911,29 +1944,29 @@
         <v>46203</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E13="",0,TIMEVALUE(F13)-TIMEVALUE(E13)))+(IF(G13="",0,TIMEVALUE(H13)-TIMEVALUE(G13))))*24,2),"")</f>
         <v/>
       </c>
       <c r="J13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="1:10">
@@ -1944,29 +1977,29 @@
         <v>46203</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="7" t="str">
         <f>IFERROR(ROUND(((IF(E14="",0,TIMEVALUE(F14)-TIMEVALUE(E14)))+(IF(G14="",0,TIMEVALUE(H14)-TIMEVALUE(G14))))*24,2),"")</f>
         <v/>
       </c>
       <c r="J14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="1:10">
@@ -1977,29 +2010,29 @@
         <v>46203</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E15="",0,TIMEVALUE(F15)-TIMEVALUE(E15)))+(IF(G15="",0,TIMEVALUE(H15)-TIMEVALUE(G15))))*24,2),"")</f>
         <v/>
       </c>
       <c r="J15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1" spans="1:10">
@@ -2022,29 +2055,29 @@
         <v>46204</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="4">
         <f>IFERROR(ROUND(((IF(E17="",0,TIMEVALUE(F17)-TIMEVALUE(E17)))+(IF(G17="",0,TIMEVALUE(H17)-TIMEVALUE(G17))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="1:10">
@@ -2055,29 +2088,29 @@
         <v>46204</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="7">
         <f>IFERROR(ROUND(((IF(E18="",0,TIMEVALUE(F18)-TIMEVALUE(E18)))+(IF(G18="",0,TIMEVALUE(H18)-TIMEVALUE(G18))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="1:10">
@@ -2088,29 +2121,29 @@
         <v>46204</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="4">
         <f>IFERROR(ROUND(((IF(E19="",0,TIMEVALUE(F19)-TIMEVALUE(E19)))+(IF(G19="",0,TIMEVALUE(H19)-TIMEVALUE(G19))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="1:10">
@@ -2121,29 +2154,29 @@
         <v>46204</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I20" s="7">
         <f>IFERROR(ROUND(((IF(E20="",0,TIMEVALUE(F20)-TIMEVALUE(E20)))+(IF(G20="",0,TIMEVALUE(H20)-TIMEVALUE(G20))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="1:10">
@@ -2154,29 +2187,29 @@
         <v>46204</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="4">
         <f>IFERROR(ROUND(((IF(E21="",0,TIMEVALUE(F21)-TIMEVALUE(E21)))+(IF(G21="",0,TIMEVALUE(H21)-TIMEVALUE(G21))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1" spans="1:10">
@@ -2199,29 +2232,29 @@
         <v>46205</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="4">
         <f>IFERROR(ROUND(((IF(E23="",0,TIMEVALUE(F23)-TIMEVALUE(E23)))+(IF(G23="",0,TIMEVALUE(H23)-TIMEVALUE(G23))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="1:10">
@@ -2232,29 +2265,29 @@
         <v>46205</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="7">
         <f>IFERROR(ROUND(((IF(E24="",0,TIMEVALUE(F24)-TIMEVALUE(E24)))+(IF(G24="",0,TIMEVALUE(H24)-TIMEVALUE(G24))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="1:10">
@@ -2265,29 +2298,29 @@
         <v>46205</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="4">
         <f>IFERROR(ROUND(((IF(E25="",0,TIMEVALUE(F25)-TIMEVALUE(E25)))+(IF(G25="",0,TIMEVALUE(H25)-TIMEVALUE(G25))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="1:10">
@@ -2298,29 +2331,29 @@
         <v>46205</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="7">
         <f>IFERROR(ROUND(((IF(E26="",0,TIMEVALUE(F26)-TIMEVALUE(E26)))+(IF(G26="",0,TIMEVALUE(H26)-TIMEVALUE(G26))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="1:10">
@@ -2331,29 +2364,29 @@
         <v>46205</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="4">
         <f>IFERROR(ROUND(((IF(E27="",0,TIMEVALUE(F27)-TIMEVALUE(E27)))+(IF(G27="",0,TIMEVALUE(H27)-TIMEVALUE(G27))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="8" customHeight="1" spans="1:10">
@@ -2376,29 +2409,29 @@
         <v>46206</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="4">
         <f>IFERROR(ROUND(((IF(E29="",0,TIMEVALUE(F29)-TIMEVALUE(E29)))+(IF(G29="",0,TIMEVALUE(H29)-TIMEVALUE(G29))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="1:10">
@@ -2409,29 +2442,29 @@
         <v>46206</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="7">
         <f>IFERROR(ROUND(((IF(E30="",0,TIMEVALUE(F30)-TIMEVALUE(E30)))+(IF(G30="",0,TIMEVALUE(H30)-TIMEVALUE(G30))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="1:10">
@@ -2442,29 +2475,29 @@
         <v>46206</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="4">
         <f>IFERROR(ROUND(((IF(E31="",0,TIMEVALUE(F31)-TIMEVALUE(E31)))+(IF(G31="",0,TIMEVALUE(H31)-TIMEVALUE(G31))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="1:10">
@@ -2475,29 +2508,29 @@
         <v>46206</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="7">
         <f>IFERROR(ROUND(((IF(E32="",0,TIMEVALUE(F32)-TIMEVALUE(E32)))+(IF(G32="",0,TIMEVALUE(H32)-TIMEVALUE(G32))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="1:10">
@@ -2508,29 +2541,29 @@
         <v>46206</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I33" s="4">
         <f>IFERROR(ROUND(((IF(E33="",0,TIMEVALUE(F33)-TIMEVALUE(E33)))+(IF(G33="",0,TIMEVALUE(H33)-TIMEVALUE(G33))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="8" customHeight="1" spans="1:10">
@@ -2553,29 +2586,29 @@
         <v>46207</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I35" s="4">
         <f>IFERROR(ROUND(((IF(E35="",0,TIMEVALUE(F35)-TIMEVALUE(E35)))+(IF(G35="",0,TIMEVALUE(H35)-TIMEVALUE(G35))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="1:10">
@@ -2586,29 +2619,29 @@
         <v>46207</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="7">
         <f>IFERROR(ROUND(((IF(E36="",0,TIMEVALUE(F36)-TIMEVALUE(E36)))+(IF(G36="",0,TIMEVALUE(H36)-TIMEVALUE(G36))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="1:10">
@@ -2619,29 +2652,29 @@
         <v>46207</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I37" s="4">
         <f>IFERROR(ROUND(((IF(E37="",0,TIMEVALUE(F37)-TIMEVALUE(E37)))+(IF(G37="",0,TIMEVALUE(H37)-TIMEVALUE(G37))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="1:10">
@@ -2652,29 +2685,29 @@
         <v>46207</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="7">
         <f>IFERROR(ROUND(((IF(E38="",0,TIMEVALUE(F38)-TIMEVALUE(E38)))+(IF(G38="",0,TIMEVALUE(H38)-TIMEVALUE(G38))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="1:10">
@@ -2685,29 +2718,29 @@
         <v>46207</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I39" s="4">
         <f>IFERROR(ROUND(((IF(E39="",0,TIMEVALUE(F39)-TIMEVALUE(E39)))+(IF(G39="",0,TIMEVALUE(H39)-TIMEVALUE(G39))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" ht="8" customHeight="1" spans="1:10">
@@ -2730,29 +2763,29 @@
         <v>46208</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I41" s="4">
         <f>IFERROR(ROUND(((IF(E41="",0,TIMEVALUE(F41)-TIMEVALUE(E41)))+(IF(G41="",0,TIMEVALUE(H41)-TIMEVALUE(G41))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="1:10">
@@ -2763,29 +2796,29 @@
         <v>46208</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I42" s="7">
         <f>IFERROR(ROUND(((IF(E42="",0,TIMEVALUE(F42)-TIMEVALUE(E42)))+(IF(G42="",0,TIMEVALUE(H42)-TIMEVALUE(G42))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" ht="14.5" spans="1:10">
@@ -2796,29 +2829,29 @@
         <v>46208</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I43" s="4">
         <f>IFERROR(ROUND(((IF(E43="",0,TIMEVALUE(F43)-TIMEVALUE(E43)))+(IF(G43="",0,TIMEVALUE(H43)-TIMEVALUE(G43))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" ht="14.5" spans="1:10">
@@ -2829,29 +2862,29 @@
         <v>46208</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I44" s="7">
         <f>IFERROR(ROUND(((IF(E44="",0,TIMEVALUE(F44)-TIMEVALUE(E44)))+(IF(G44="",0,TIMEVALUE(H44)-TIMEVALUE(G44))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" ht="14.5" spans="1:10">
@@ -2862,29 +2895,29 @@
         <v>46208</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I45" s="4">
         <f>IFERROR(ROUND(((IF(E45="",0,TIMEVALUE(F45)-TIMEVALUE(E45)))+(IF(G45="",0,TIMEVALUE(H45)-TIMEVALUE(G45))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" ht="8" customHeight="1" spans="1:10">
@@ -2907,29 +2940,29 @@
         <v>46209</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I47" s="4">
         <f>IFERROR(ROUND(((IF(E47="",0,TIMEVALUE(F47)-TIMEVALUE(E47)))+(IF(G47="",0,TIMEVALUE(H47)-TIMEVALUE(G47))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="1:10">
@@ -2940,29 +2973,29 @@
         <v>46209</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I48" s="7">
         <f>IFERROR(ROUND(((IF(E48="",0,TIMEVALUE(F48)-TIMEVALUE(E48)))+(IF(G48="",0,TIMEVALUE(H48)-TIMEVALUE(G48))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="1:10">
@@ -2973,29 +3006,29 @@
         <v>46209</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I49" s="4">
         <f>IFERROR(ROUND(((IF(E49="",0,TIMEVALUE(F49)-TIMEVALUE(E49)))+(IF(G49="",0,TIMEVALUE(H49)-TIMEVALUE(G49))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="1:10">
@@ -3006,29 +3039,29 @@
         <v>46209</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I50" s="7">
         <f>IFERROR(ROUND(((IF(E50="",0,TIMEVALUE(F50)-TIMEVALUE(E50)))+(IF(G50="",0,TIMEVALUE(H50)-TIMEVALUE(G50))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="1:10">
@@ -3039,29 +3072,29 @@
         <v>46209</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I51" s="4">
         <f>IFERROR(ROUND(((IF(E51="",0,TIMEVALUE(F51)-TIMEVALUE(E51)))+(IF(G51="",0,TIMEVALUE(H51)-TIMEVALUE(G51))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" ht="8" customHeight="1" spans="1:10">
@@ -3084,29 +3117,29 @@
         <v>46210</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I53" s="4">
         <f>IFERROR(ROUND(((IF(E53="",0,TIMEVALUE(F53)-TIMEVALUE(E53)))+(IF(G53="",0,TIMEVALUE(H53)-TIMEVALUE(G53))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" ht="14.5" spans="1:10">
@@ -3117,29 +3150,29 @@
         <v>46210</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I54" s="7">
         <f>IFERROR(ROUND(((IF(E54="",0,TIMEVALUE(F54)-TIMEVALUE(E54)))+(IF(G54="",0,TIMEVALUE(H54)-TIMEVALUE(G54))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" ht="14.5" spans="1:10">
@@ -3150,29 +3183,29 @@
         <v>46210</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I55" s="4">
         <f>IFERROR(ROUND(((IF(E55="",0,TIMEVALUE(F55)-TIMEVALUE(E55)))+(IF(G55="",0,TIMEVALUE(H55)-TIMEVALUE(G55))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" ht="14.5" spans="1:10">
@@ -3183,29 +3216,29 @@
         <v>46210</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I56" s="7">
         <f>IFERROR(ROUND(((IF(E56="",0,TIMEVALUE(F56)-TIMEVALUE(E56)))+(IF(G56="",0,TIMEVALUE(H56)-TIMEVALUE(G56))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" ht="14.5" spans="1:10">
@@ -3216,29 +3249,29 @@
         <v>46210</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I57" s="4">
         <f>IFERROR(ROUND(((IF(E57="",0,TIMEVALUE(F57)-TIMEVALUE(E57)))+(IF(G57="",0,TIMEVALUE(H57)-TIMEVALUE(G57))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" ht="8" customHeight="1" spans="1:10">
@@ -3261,29 +3294,29 @@
         <v>46211</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I59" s="4">
         <f>IFERROR(ROUND(((IF(E59="",0,TIMEVALUE(F59)-TIMEVALUE(E59)))+(IF(G59="",0,TIMEVALUE(H59)-TIMEVALUE(G59))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="1:10">
@@ -3294,29 +3327,29 @@
         <v>46211</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I60" s="7">
         <f>IFERROR(ROUND(((IF(E60="",0,TIMEVALUE(F60)-TIMEVALUE(E60)))+(IF(G60="",0,TIMEVALUE(H60)-TIMEVALUE(G60))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="1:10">
@@ -3327,29 +3360,29 @@
         <v>46211</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I61" s="4">
         <f>IFERROR(ROUND(((IF(E61="",0,TIMEVALUE(F61)-TIMEVALUE(E61)))+(IF(G61="",0,TIMEVALUE(H61)-TIMEVALUE(G61))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" ht="14.5" spans="1:10">
@@ -3360,29 +3393,29 @@
         <v>46211</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I62" s="7">
         <f>IFERROR(ROUND(((IF(E62="",0,TIMEVALUE(F62)-TIMEVALUE(E62)))+(IF(G62="",0,TIMEVALUE(H62)-TIMEVALUE(G62))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" ht="14.5" spans="1:10">
@@ -3393,29 +3426,29 @@
         <v>46211</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I63" s="4">
         <f>IFERROR(ROUND(((IF(E63="",0,TIMEVALUE(F63)-TIMEVALUE(E63)))+(IF(G63="",0,TIMEVALUE(H63)-TIMEVALUE(G63))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" ht="8" customHeight="1" spans="1:10">
@@ -3438,29 +3471,29 @@
         <v>46212</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I65" s="4">
         <f>IFERROR(ROUND(((IF(E65="",0,TIMEVALUE(F65)-TIMEVALUE(E65)))+(IF(G65="",0,TIMEVALUE(H65)-TIMEVALUE(G65))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" ht="14.5" spans="1:10">
@@ -3471,29 +3504,29 @@
         <v>46212</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I66" s="7">
         <f>IFERROR(ROUND(((IF(E66="",0,TIMEVALUE(F66)-TIMEVALUE(E66)))+(IF(G66="",0,TIMEVALUE(H66)-TIMEVALUE(G66))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" ht="14.5" spans="1:10">
@@ -3504,29 +3537,29 @@
         <v>46212</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I67" s="4">
         <f>IFERROR(ROUND(((IF(E67="",0,TIMEVALUE(F67)-TIMEVALUE(E67)))+(IF(G67="",0,TIMEVALUE(H67)-TIMEVALUE(G67))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" ht="14.5" spans="1:10">
@@ -3537,29 +3570,29 @@
         <v>46212</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I68" s="7">
         <f>IFERROR(ROUND(((IF(E68="",0,TIMEVALUE(F68)-TIMEVALUE(E68)))+(IF(G68="",0,TIMEVALUE(H68)-TIMEVALUE(G68))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" ht="14.5" spans="1:10">
@@ -3570,29 +3603,29 @@
         <v>46212</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I69" s="4">
         <f>IFERROR(ROUND(((IF(E69="",0,TIMEVALUE(F69)-TIMEVALUE(E69)))+(IF(G69="",0,TIMEVALUE(H69)-TIMEVALUE(G69))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" ht="8" customHeight="1" spans="1:10">
@@ -3615,29 +3648,29 @@
         <v>46213</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I71" s="4">
         <f>IFERROR(ROUND(((IF(E71="",0,TIMEVALUE(F71)-TIMEVALUE(E71)))+(IF(G71="",0,TIMEVALUE(H71)-TIMEVALUE(G71))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" ht="14.5" spans="1:10">
@@ -3648,29 +3681,29 @@
         <v>46213</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I72" s="7">
         <f>IFERROR(ROUND(((IF(E72="",0,TIMEVALUE(F72)-TIMEVALUE(E72)))+(IF(G72="",0,TIMEVALUE(H72)-TIMEVALUE(G72))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" ht="14.5" spans="1:10">
@@ -3681,29 +3714,29 @@
         <v>46213</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I73" s="4">
         <f>IFERROR(ROUND(((IF(E73="",0,TIMEVALUE(F73)-TIMEVALUE(E73)))+(IF(G73="",0,TIMEVALUE(H73)-TIMEVALUE(G73))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" ht="14.5" spans="1:10">
@@ -3714,29 +3747,29 @@
         <v>46213</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I74" s="7">
         <f>IFERROR(ROUND(((IF(E74="",0,TIMEVALUE(F74)-TIMEVALUE(E74)))+(IF(G74="",0,TIMEVALUE(H74)-TIMEVALUE(G74))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" ht="14.5" spans="1:10">
@@ -3747,29 +3780,29 @@
         <v>46213</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I75" s="4">
         <f>IFERROR(ROUND(((IF(E75="",0,TIMEVALUE(F75)-TIMEVALUE(E75)))+(IF(G75="",0,TIMEVALUE(H75)-TIMEVALUE(G75))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" ht="8" customHeight="1" spans="1:10">
@@ -3792,29 +3825,29 @@
         <v>46214</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I77" s="4">
         <f>IFERROR(ROUND(((IF(E77="",0,TIMEVALUE(F77)-TIMEVALUE(E77)))+(IF(G77="",0,TIMEVALUE(H77)-TIMEVALUE(G77))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" ht="14.5" spans="1:10">
@@ -3825,29 +3858,29 @@
         <v>46214</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I78" s="7">
         <f>IFERROR(ROUND(((IF(E78="",0,TIMEVALUE(F78)-TIMEVALUE(E78)))+(IF(G78="",0,TIMEVALUE(H78)-TIMEVALUE(G78))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" ht="14.5" spans="1:10">
@@ -3858,29 +3891,29 @@
         <v>46214</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I79" s="4">
         <f>IFERROR(ROUND(((IF(E79="",0,TIMEVALUE(F79)-TIMEVALUE(E79)))+(IF(G79="",0,TIMEVALUE(H79)-TIMEVALUE(G79))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" ht="14.5" spans="1:10">
@@ -3891,29 +3924,29 @@
         <v>46214</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I80" s="7">
         <f>IFERROR(ROUND(((IF(E80="",0,TIMEVALUE(F80)-TIMEVALUE(E80)))+(IF(G80="",0,TIMEVALUE(H80)-TIMEVALUE(G80))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" ht="14.5" spans="1:10">
@@ -3924,29 +3957,29 @@
         <v>46214</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I81" s="4">
         <f>IFERROR(ROUND(((IF(E81="",0,TIMEVALUE(F81)-TIMEVALUE(E81)))+(IF(G81="",0,TIMEVALUE(H81)-TIMEVALUE(G81))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" ht="8" customHeight="1" spans="1:10">
@@ -3969,29 +4002,29 @@
         <v>46215</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I83" s="4">
         <f>IFERROR(ROUND(((IF(E83="",0,TIMEVALUE(F83)-TIMEVALUE(E83)))+(IF(G83="",0,TIMEVALUE(H83)-TIMEVALUE(G83))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" ht="14.5" spans="1:10">
@@ -4002,29 +4035,29 @@
         <v>46215</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I84" s="7">
         <f>IFERROR(ROUND(((IF(E84="",0,TIMEVALUE(F84)-TIMEVALUE(E84)))+(IF(G84="",0,TIMEVALUE(H84)-TIMEVALUE(G84))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" ht="14.5" spans="1:10">
@@ -4035,29 +4068,29 @@
         <v>46215</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I85" s="4">
         <f>IFERROR(ROUND(((IF(E85="",0,TIMEVALUE(F85)-TIMEVALUE(E85)))+(IF(G85="",0,TIMEVALUE(H85)-TIMEVALUE(G85))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" ht="14.5" spans="1:10">
@@ -4068,29 +4101,29 @@
         <v>46215</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I86" s="7">
         <f>IFERROR(ROUND(((IF(E86="",0,TIMEVALUE(F86)-TIMEVALUE(E86)))+(IF(G86="",0,TIMEVALUE(H86)-TIMEVALUE(G86))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" ht="14.5" spans="1:10">
@@ -4101,29 +4134,29 @@
         <v>46215</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I87" s="4">
         <f>IFERROR(ROUND(((IF(E87="",0,TIMEVALUE(F87)-TIMEVALUE(E87)))+(IF(G87="",0,TIMEVALUE(H87)-TIMEVALUE(G87))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" ht="8" customHeight="1" spans="1:10">
@@ -4146,29 +4179,29 @@
         <v>46216</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I89" s="4">
         <f>IFERROR(ROUND(((IF(E89="",0,TIMEVALUE(F89)-TIMEVALUE(E89)))+(IF(G89="",0,TIMEVALUE(H89)-TIMEVALUE(G89))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" ht="14.5" spans="1:10">
@@ -4179,29 +4212,29 @@
         <v>46216</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I90" s="7">
         <f>IFERROR(ROUND(((IF(E90="",0,TIMEVALUE(F90)-TIMEVALUE(E90)))+(IF(G90="",0,TIMEVALUE(H90)-TIMEVALUE(G90))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" ht="14.5" spans="1:10">
@@ -4212,29 +4245,29 @@
         <v>46216</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I91" s="4">
         <f>IFERROR(ROUND(((IF(E91="",0,TIMEVALUE(F91)-TIMEVALUE(E91)))+(IF(G91="",0,TIMEVALUE(H91)-TIMEVALUE(G91))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" ht="14.5" spans="1:10">
@@ -4245,29 +4278,29 @@
         <v>46216</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I92" s="7">
         <f>IFERROR(ROUND(((IF(E92="",0,TIMEVALUE(F92)-TIMEVALUE(E92)))+(IF(G92="",0,TIMEVALUE(H92)-TIMEVALUE(G92))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" ht="14.5" spans="1:10">
@@ -4278,29 +4311,29 @@
         <v>46216</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I93" s="4">
         <f>IFERROR(ROUND(((IF(E93="",0,TIMEVALUE(F93)-TIMEVALUE(E93)))+(IF(G93="",0,TIMEVALUE(H93)-TIMEVALUE(G93))))*24,2),"")</f>
         <v>0</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" ht="8" customHeight="1" spans="1:10">
@@ -4347,12 +4380,12 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11">
@@ -4360,10 +4393,10 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
@@ -4372,22 +4405,22 @@
         <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" ht="14.5" spans="1:11">
@@ -4398,31 +4431,31 @@
         <v>46202</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="1:11">
@@ -4433,31 +4466,31 @@
         <v>46202</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="14.5" spans="1:11">
@@ -4468,31 +4501,31 @@
         <v>46202</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="1:11">
@@ -4503,31 +4536,31 @@
         <v>46202</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="1:11">
@@ -4538,31 +4571,31 @@
         <v>46202</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="8" customHeight="1" spans="1:11">
@@ -4586,31 +4619,31 @@
         <v>46203</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="1:11">
@@ -4621,31 +4654,31 @@
         <v>46203</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:11">
@@ -4656,31 +4689,31 @@
         <v>46203</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="1:11">
@@ -4691,31 +4724,31 @@
         <v>46203</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="1:11">
@@ -4726,31 +4759,31 @@
         <v>46203</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1" spans="1:11">
@@ -4774,31 +4807,31 @@
         <v>46204</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="1:11">
@@ -4809,31 +4842,31 @@
         <v>46204</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="1:11">
@@ -4844,31 +4877,31 @@
         <v>46204</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="1:11">
@@ -4879,31 +4912,31 @@
         <v>46204</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="1:11">
@@ -4914,31 +4947,31 @@
         <v>46204</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1" spans="1:11">
@@ -4962,31 +4995,31 @@
         <v>46205</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="1:11">
@@ -4997,31 +5030,31 @@
         <v>46205</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="1:11">
@@ -5032,31 +5065,31 @@
         <v>46205</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="1:11">
@@ -5067,31 +5100,31 @@
         <v>46205</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="1:11">
@@ -5102,31 +5135,31 @@
         <v>46205</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="8" customHeight="1" spans="1:11">
@@ -5150,31 +5183,31 @@
         <v>46206</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="1:11">
@@ -5185,31 +5218,31 @@
         <v>46206</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="1:11">
@@ -5220,31 +5253,31 @@
         <v>46206</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="1:11">
@@ -5255,31 +5288,31 @@
         <v>46206</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="1:11">
@@ -5290,31 +5323,31 @@
         <v>46206</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="8" customHeight="1" spans="1:11">
@@ -5338,31 +5371,31 @@
         <v>46207</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" ht="14.5" spans="1:11">
@@ -5373,31 +5406,31 @@
         <v>46207</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="1:11">
@@ -5408,31 +5441,31 @@
         <v>46207</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="1:11">
@@ -5443,31 +5476,31 @@
         <v>46207</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" ht="14.5" spans="1:11">
@@ -5478,31 +5511,31 @@
         <v>46207</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" ht="8" customHeight="1" spans="1:11">
@@ -5526,31 +5559,31 @@
         <v>46208</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" ht="14.5" spans="1:11">
@@ -5561,31 +5594,31 @@
         <v>46208</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" ht="14.5" spans="1:11">
@@ -5596,31 +5629,31 @@
         <v>46208</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" ht="14.5" spans="1:11">
@@ -5631,31 +5664,31 @@
         <v>46208</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" ht="14.5" spans="1:11">
@@ -5666,31 +5699,31 @@
         <v>46208</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" ht="8" customHeight="1" spans="1:11">
@@ -5714,31 +5747,31 @@
         <v>46209</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="1:11">
@@ -5749,31 +5782,31 @@
         <v>46209</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="1:11">
@@ -5784,31 +5817,31 @@
         <v>46209</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="1:11">
@@ -5819,31 +5852,31 @@
         <v>46209</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="1:11">
@@ -5854,31 +5887,31 @@
         <v>46209</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" ht="8" customHeight="1" spans="1:11">
@@ -5902,31 +5935,31 @@
         <v>46210</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" ht="14.5" spans="1:11">
@@ -5937,31 +5970,31 @@
         <v>46210</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" ht="14.5" spans="1:11">
@@ -5972,31 +6005,31 @@
         <v>46210</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" ht="14.5" spans="1:11">
@@ -6007,31 +6040,31 @@
         <v>46210</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" ht="14.5" spans="1:11">
@@ -6042,31 +6075,31 @@
         <v>46210</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" ht="8" customHeight="1" spans="1:11">
@@ -6090,31 +6123,31 @@
         <v>46211</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="1:11">
@@ -6125,31 +6158,31 @@
         <v>46211</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="1:11">
@@ -6160,31 +6193,31 @@
         <v>46211</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" ht="14.5" spans="1:11">
@@ -6195,31 +6228,31 @@
         <v>46211</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" ht="14.5" spans="1:11">
@@ -6230,31 +6263,31 @@
         <v>46211</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" ht="8" customHeight="1" spans="1:11">
@@ -6278,31 +6311,31 @@
         <v>46212</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" ht="14.5" spans="1:11">
@@ -6313,31 +6346,31 @@
         <v>46212</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" ht="14.5" spans="1:11">
@@ -6348,31 +6381,31 @@
         <v>46212</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" ht="14.5" spans="1:11">
@@ -6383,31 +6416,31 @@
         <v>46212</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" ht="14.5" spans="1:11">
@@ -6418,31 +6451,31 @@
         <v>46212</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" ht="8" customHeight="1" spans="1:11">
@@ -6466,31 +6499,31 @@
         <v>46213</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" ht="14.5" spans="1:11">
@@ -6501,31 +6534,31 @@
         <v>46213</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" ht="14.5" spans="1:11">
@@ -6536,31 +6569,31 @@
         <v>46213</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" ht="14.5" spans="1:11">
@@ -6571,31 +6604,31 @@
         <v>46213</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" ht="14.5" spans="1:11">
@@ -6606,31 +6639,31 @@
         <v>46213</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" ht="8" customHeight="1" spans="1:11">
@@ -6654,31 +6687,31 @@
         <v>46214</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" ht="14.5" spans="1:11">
@@ -6689,31 +6722,31 @@
         <v>46214</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" ht="14.5" spans="1:11">
@@ -6724,31 +6757,31 @@
         <v>46214</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" ht="14.5" spans="1:11">
@@ -6759,31 +6792,31 @@
         <v>46214</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" ht="14.5" spans="1:11">
@@ -6794,31 +6827,31 @@
         <v>46214</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" ht="8" customHeight="1" spans="1:11">
@@ -6842,31 +6875,31 @@
         <v>46215</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" ht="14.5" spans="1:11">
@@ -6877,31 +6910,31 @@
         <v>46215</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" ht="14.5" spans="1:11">
@@ -6912,31 +6945,31 @@
         <v>46215</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" ht="14.5" spans="1:11">
@@ -6947,31 +6980,31 @@
         <v>46215</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" ht="14.5" spans="1:11">
@@ -6982,31 +7015,31 @@
         <v>46215</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" ht="8" customHeight="1" spans="1:11">
@@ -7030,31 +7063,31 @@
         <v>46216</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" ht="14.5" spans="1:11">
@@ -7065,31 +7098,31 @@
         <v>46216</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" ht="14.5" spans="1:11">
@@ -7100,31 +7133,31 @@
         <v>46216</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" ht="14.5" spans="1:11">
@@ -7135,31 +7168,31 @@
         <v>46216</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" ht="14.5" spans="1:11">
@@ -7170,31 +7203,31 @@
         <v>46216</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" ht="8" customHeight="1" spans="1:11">
@@ -7241,12 +7274,12 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11">
@@ -7254,69 +7287,69 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" ht="14.5" spans="1:11">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" ht="29" spans="1:11">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="14.5" spans="1:11">
@@ -7324,69 +7357,69 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" ht="14.5" spans="1:11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="29" spans="1:11">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="14.5" spans="1:11">
@@ -7394,34 +7427,34 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="14.5" spans="1:11">
@@ -7429,34 +7462,34 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="14.5" spans="1:11">
@@ -7464,34 +7497,34 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="14.5" spans="1:11">
@@ -7499,34 +7532,34 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="1:11">
@@ -7534,34 +7567,34 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:11">
@@ -7569,34 +7602,34 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="14.5" spans="1:11">
@@ -7604,34 +7637,34 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="14.5" spans="1:11">
@@ -7639,34 +7672,34 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="14.5" spans="1:11">
@@ -7674,34 +7707,34 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="14.5" spans="1:11">
@@ -7709,34 +7742,34 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="14.5" spans="1:11">
@@ -7744,34 +7777,34 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="14.5" spans="1:11">
@@ -7779,34 +7812,34 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="14.5" spans="1:11">
@@ -7814,34 +7847,34 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="14.5" spans="1:11">
@@ -7849,34 +7882,34 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="14.5" spans="1:11">
@@ -7884,34 +7917,34 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="14.5" spans="1:11">
@@ -7919,34 +7952,34 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="14.5" spans="1:11">
@@ -7954,34 +7987,34 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="14.5" spans="1:11">
@@ -7989,34 +8022,34 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="14.5" spans="1:11">
@@ -8024,34 +8057,34 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="14.5" spans="1:11">
@@ -8059,34 +8092,34 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="14.5" spans="1:11">
@@ -8094,34 +8127,34 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" ht="14.5" spans="1:11">
@@ -8129,34 +8162,34 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="14.5" spans="1:11">
@@ -8164,34 +8197,34 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="14.5" spans="1:11">
@@ -8199,34 +8232,34 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="14.5" spans="1:11">
@@ -8234,34 +8267,34 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="14.5" spans="1:11">
@@ -8269,34 +8302,34 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" ht="14.5" spans="1:11">
@@ -8304,34 +8337,34 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/文档/项目组考勤与开发日志.xlsx
+++ b/文档/项目组考勤与开发日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="110">
   <si>
     <t>智慧烟感项目 · 考勤与开发日志表 使用说明</t>
   </si>
@@ -255,6 +255,45 @@
     <t>次日计划</t>
   </si>
   <si>
+    <t>原型设计</t>
+  </si>
+  <si>
+    <t>原型设计，用户画像，需求分析</t>
+  </si>
+  <si>
+    <t>未完成</t>
+  </si>
+  <si>
+    <t>没有明确需求</t>
+  </si>
+  <si>
+    <t>明确需求，打通硬件、后端、前端简单的通路</t>
+  </si>
+  <si>
+    <t>配置硬件环境，跑通hello world</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>实现mqtt数据传输</t>
+  </si>
+  <si>
+    <t>数据库</t>
+  </si>
+  <si>
+    <t>建表</t>
+  </si>
+  <si>
+    <t>前端设计</t>
+  </si>
+  <si>
+    <t>设计主页面，原型设计</t>
+  </si>
+  <si>
+    <t>配置springboot，理解接口概念</t>
+  </si>
+  <si>
     <t>智慧烟感项目 · 任务清单</t>
   </si>
   <si>
@@ -294,7 +333,7 @@
     <t>设计原型</t>
   </si>
   <si>
-    <t>明确各个模块的细节，交互逻辑和API接口</t>
+    <t>明确各个模块的细节，交互逻辑和API接口调用，比如每个模块包含哪些具体信息，具体状态，设计思路，</t>
   </si>
   <si>
     <t>高</t>
@@ -306,10 +345,40 @@
     <t>下载硬件环境，跑通硬件</t>
   </si>
   <si>
+    <t>配置环境</t>
+  </si>
+  <si>
     <t>后端配置环境</t>
   </si>
   <si>
+    <t>spring boot框架，MySQL</t>
+  </si>
+  <si>
     <t>郑良锋、王田煜</t>
+  </si>
+  <si>
+    <t>书写接口文档</t>
+  </si>
+  <si>
+    <t>把接口类型，请求参数，响应结果写好</t>
+  </si>
+  <si>
+    <t>数据库建表</t>
+  </si>
+  <si>
+    <t>创建了8个表</t>
+  </si>
+  <si>
+    <t>完成接口代码</t>
+  </si>
+  <si>
+    <t>解决mqtt数据传输</t>
+  </si>
+  <si>
+    <t>前端完善交互细节</t>
+  </si>
+  <si>
+    <t>后端逻辑设计</t>
   </si>
 </sst>
 </file>
@@ -323,7 +392,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,13 +433,6 @@
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -517,7 +579,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,12 +619,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,28 +915,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,37 +948,37 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -934,73 +993,70 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1887,17 +1943,16 @@
         <v>53</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="4" t="str">
-        <f>IFERROR(ROUND(((IF(E11="",0,TIMEVALUE(F11)-TIMEVALUE(E11)))+(IF(G11="",0,TIMEVALUE(H11)-TIMEVALUE(G11))))*24,2),"")</f>
-        <v/>
+        <v>53</v>
+      </c>
+      <c r="I11" s="4">
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>33</v>
@@ -1919,18 +1974,17 @@
       <c r="E12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="7" t="str">
-        <f>IFERROR(ROUND(((IF(E12="",0,TIMEVALUE(F12)-TIMEVALUE(E12)))+(IF(G12="",0,TIMEVALUE(H12)-TIMEVALUE(G12))))*24,2),"")</f>
-        <v/>
+      <c r="F12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="7">
+        <v>8</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>33</v>
@@ -1953,17 +2007,16 @@
         <v>53</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="4" t="str">
-        <f>IFERROR(ROUND(((IF(E13="",0,TIMEVALUE(F13)-TIMEVALUE(E13)))+(IF(G13="",0,TIMEVALUE(H13)-TIMEVALUE(G13))))*24,2),"")</f>
-        <v/>
+        <v>53</v>
+      </c>
+      <c r="I13" s="4">
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>33</v>
@@ -1985,18 +2038,17 @@
       <c r="E14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="7" t="str">
-        <f>IFERROR(ROUND(((IF(E14="",0,TIMEVALUE(F14)-TIMEVALUE(E14)))+(IF(G14="",0,TIMEVALUE(H14)-TIMEVALUE(G14))))*24,2),"")</f>
-        <v/>
+      <c r="F14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="7">
+        <v>8</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>33</v>
@@ -2019,17 +2071,16 @@
         <v>53</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="4" t="str">
-        <f>IFERROR(ROUND(((IF(E15="",0,TIMEVALUE(F15)-TIMEVALUE(E15)))+(IF(G15="",0,TIMEVALUE(H15)-TIMEVALUE(G15))))*24,2),"")</f>
-        <v/>
+        <v>53</v>
+      </c>
+      <c r="I15" s="4">
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>33</v>
@@ -4611,7 +4662,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" ht="14.5" spans="1:11">
+    <row r="11" ht="29" spans="1:11">
       <c r="A11" s="4">
         <v>6</v>
       </c>
@@ -4625,13 +4676,13 @@
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>33</v>
@@ -4640,10 +4691,10 @@
         <v>33</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="14.5" spans="1:11">
@@ -4660,13 +4711,13 @@
         <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>33</v>
@@ -4674,11 +4725,9 @@
       <c r="I12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="J12" s="7"/>
       <c r="K12" s="7" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:11">
@@ -4695,13 +4744,13 @@
         <v>37</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>33</v>
@@ -4712,9 +4761,7 @@
       <c r="J13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" ht="14.5" spans="1:11">
       <c r="A14" s="7">
@@ -4730,13 +4777,13 @@
         <v>39</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>33</v>
@@ -4765,13 +4812,13 @@
         <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>33</v>
@@ -7274,12 +7321,12 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11">
@@ -7287,45 +7334,45 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" ht="29" spans="1:11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" ht="43.5" spans="1:11">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>39</v>
@@ -7334,13 +7381,13 @@
         <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>33</v>
+        <v>96</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46203</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>33</v>
@@ -7357,10 +7404,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>34</v>
@@ -7369,13 +7416,13 @@
         <v>33</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>33</v>
+        <v>96</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46203</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>33</v>
@@ -7392,25 +7439,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>33</v>
+        <v>96</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46203</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>33</v>
@@ -7427,10 +7474,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>33</v>
@@ -7457,18 +7504,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="1:11">
+    <row r="9" ht="29" spans="1:11">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>33</v>
@@ -7497,13 +7544,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
@@ -7532,13 +7579,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>33</v>
@@ -7567,13 +7614,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>33</v>
@@ -7602,7 +7649,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>33</v>

--- a/文档/项目组考勤与开发日志.xlsx
+++ b/文档/项目组考勤与开发日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
+    <workbookView windowWidth="25600" windowHeight="11630" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="116">
   <si>
     <t>智慧烟感项目 · 考勤与开发日志表 使用说明</t>
   </si>
@@ -294,6 +294,19 @@
     <t>配置springboot，理解接口概念</t>
   </si>
   <si>
+    <t>完成在BearPi-HM_Nano开发板上使用MQTT协议</t>
+  </si>
+  <si>
+    <t>1、了解mqtt协议原理
+2、从mqtt broker到数据库数据传输部分的部分编写</t>
+  </si>
+  <si>
+    <t>1.将前端代码改成vue语言2.了解css语言</t>
+  </si>
+  <si>
+    <t>1、完善昨天的代码测试2、更新GitHub文档</t>
+  </si>
+  <si>
     <t>智慧烟感项目 · 任务清单</t>
   </si>
   <si>
@@ -378,7 +391,13 @@
     <t>前端完善交互细节</t>
   </si>
   <si>
-    <t>后端逻辑设计</t>
+    <t>中</t>
+  </si>
+  <si>
+    <t>测试前后端数据能否打通</t>
+  </si>
+  <si>
+    <t>王田煜、郑良锋、陈心澄</t>
   </si>
 </sst>
 </file>
@@ -2112,10 +2131,10 @@
         <v>30</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>33</v>
@@ -2123,9 +2142,9 @@
       <c r="H17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E17="",0,TIMEVALUE(F17)-TIMEVALUE(E17)))+(IF(G17="",0,TIMEVALUE(H17)-TIMEVALUE(G17))))*24,2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J17" s="4" t="s">
         <v>33</v>
@@ -2144,11 +2163,11 @@
       <c r="D18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>33</v>
+      <c r="E18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>33</v>
@@ -2156,9 +2175,9 @@
       <c r="H18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="7" t="str">
         <f>IFERROR(ROUND(((IF(E18="",0,TIMEVALUE(F18)-TIMEVALUE(E18)))+(IF(G18="",0,TIMEVALUE(H18)-TIMEVALUE(G18))))*24,2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J18" s="7" t="s">
         <v>33</v>
@@ -2178,10 +2197,10 @@
         <v>37</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>33</v>
@@ -2189,9 +2208,9 @@
       <c r="H19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E19="",0,TIMEVALUE(F19)-TIMEVALUE(E19)))+(IF(G19="",0,TIMEVALUE(H19)-TIMEVALUE(G19))))*24,2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J19" s="4" t="s">
         <v>33</v>
@@ -2210,11 +2229,11 @@
       <c r="D20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>33</v>
+      <c r="E20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>33</v>
@@ -2222,9 +2241,9 @@
       <c r="H20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="7" t="str">
         <f>IFERROR(ROUND(((IF(E20="",0,TIMEVALUE(F20)-TIMEVALUE(E20)))+(IF(G20="",0,TIMEVALUE(H20)-TIMEVALUE(G20))))*24,2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J20" s="7" t="s">
         <v>33</v>
@@ -2244,10 +2263,10 @@
         <v>41</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>33</v>
@@ -2255,9 +2274,9 @@
       <c r="H21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="4" t="str">
         <f>IFERROR(ROUND(((IF(E21="",0,TIMEVALUE(F21)-TIMEVALUE(E21)))+(IF(G21="",0,TIMEVALUE(H21)-TIMEVALUE(G21))))*24,2),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J21" s="4" t="s">
         <v>33</v>
@@ -4860,7 +4879,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
@@ -4881,7 +4900,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="14.5" spans="1:11">
+    <row r="18" ht="29" spans="1:11">
       <c r="A18" s="7">
         <v>12</v>
       </c>
@@ -4895,10 +4914,10 @@
         <v>34</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>33</v>
@@ -4916,7 +4935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" ht="14.5" spans="1:11">
+    <row r="19" ht="43.5" spans="1:11">
       <c r="A19" s="4">
         <v>13</v>
       </c>
@@ -4930,10 +4949,10 @@
         <v>37</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>33</v>
@@ -4951,7 +4970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" ht="14.5" spans="1:11">
+    <row r="20" ht="29" spans="1:11">
       <c r="A20" s="7">
         <v>14</v>
       </c>
@@ -4965,10 +4984,10 @@
         <v>39</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>33</v>
@@ -4986,7 +5005,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" ht="14.5" spans="1:11">
+    <row r="21" ht="29" spans="1:11">
       <c r="A21" s="4">
         <v>15</v>
       </c>
@@ -5000,10 +5019,10 @@
         <v>41</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>33</v>
@@ -5048,7 +5067,7 @@
         <v>30</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>33</v>
@@ -5083,7 +5102,7 @@
         <v>34</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>33</v>
@@ -5118,7 +5137,7 @@
         <v>37</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>33</v>
@@ -5153,7 +5172,7 @@
         <v>39</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>33</v>
@@ -5188,7 +5207,7 @@
         <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>33</v>
@@ -5236,7 +5255,7 @@
         <v>30</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>33</v>
@@ -5271,7 +5290,7 @@
         <v>34</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>33</v>
@@ -5306,7 +5325,7 @@
         <v>37</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>33</v>
@@ -5341,7 +5360,7 @@
         <v>39</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>33</v>
@@ -5376,7 +5395,7 @@
         <v>41</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>33</v>
@@ -7321,12 +7340,12 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:11">
@@ -7334,34 +7353,34 @@
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" ht="43.5" spans="1:11">
@@ -7369,10 +7388,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>39</v>
@@ -7381,10 +7400,10 @@
         <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H5" s="5">
         <v>46203</v>
@@ -7404,22 +7423,20 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H6" s="8">
         <v>46203</v>
@@ -7439,22 +7456,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H7" s="5">
         <v>46203</v>
@@ -7474,22 +7491,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>33</v>
@@ -7509,13 +7526,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>33</v>
@@ -7544,7 +7561,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>33</v>
@@ -7579,7 +7596,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>33</v>
@@ -7614,19 +7631,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>33</v>
@@ -7644,27 +7661,27 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" ht="14.5" spans="1:11">
+    <row r="13" ht="29" spans="1:11">
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>109</v>
+      <c r="B13" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>33</v>
+      <c r="D13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>33</v>
@@ -7683,24 +7700,7 @@
       <c r="A14" s="7">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="C14" s="7"/>
       <c r="H14" s="8" t="s">
         <v>33</v>
       </c>
@@ -8423,10 +8423,10 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F13 F15:F34">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G13 G15:G34">
       <formula1>"未开始,进行中,已完成,阻塞"</formula1>
     </dataValidation>
   </dataValidations>
